--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -60,6 +60,15 @@
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -85,6 +94,15 @@
   </si>
   <si>
     <t>移动速度</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击范围</t>
   </si>
   <si>
     <t>Wizard</t>
@@ -1135,9 +1153,15 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -1210,20 +1234,26 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:36">
       <c r="A3" s="9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -1256,7 +1286,7 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:36">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1296,20 +1326,26 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:36">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1345,14 +1381,20 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="4">
         <v>100</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
       <c r="H6" s="13"/>
       <c r="J6" s="13"/>
       <c r="L6" s="13"/>

--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Godot-Project\StartFromZero\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -106,6 +111,9 @@
   </si>
   <si>
     <t>Wizard</t>
+  </si>
+  <si>
+    <t>Bug</t>
   </si>
 </sst>
 </file>
@@ -1390,10 +1398,10 @@
         <v>100</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="13"/>
       <c r="J6" s="13"/>
@@ -1402,12 +1410,24 @@
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:36">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4">
+        <v>800</v>
+      </c>
+      <c r="E7" s="4">
+        <v>80</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
       <c r="H7" s="13"/>
       <c r="J7" s="13"/>
       <c r="L7" s="13"/>
